--- a/tests/data/AutoTestData.xlsx
+++ b/tests/data/AutoTestData.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>wTJgColy</v>
       </c>
       <c r="F2" t="str">
-        <v>luna_kihn1749693381480@gmail.com</v>
+        <v>luna_kihn1749778050913@gmail.com</v>
       </c>
       <c r="G2" t="str">
         <v>PASS</v>
@@ -462,7 +462,7 @@
         <v>XqNozUGD</v>
       </c>
       <c r="F3" t="str">
-        <v>rahsaan_ruecker781749693403092@hotmail.com</v>
+        <v>rahsaan_ruecker781749778058883@hotmail.com</v>
       </c>
       <c r="G3" t="str">
         <v>PASS</v>
@@ -485,7 +485,7 @@
         <v>AAHWrgkj</v>
       </c>
       <c r="F4" t="str">
-        <v>bradford_berge1749693405774@yahoo.com</v>
+        <v>bradford_berge1749778061455@yahoo.com</v>
       </c>
       <c r="G4" t="str">
         <v>PASS</v>
@@ -508,7 +508,7 @@
         <v>qNObPY3T</v>
       </c>
       <c r="F5" t="str">
-        <v>giovanni01749693408320@gmail.com</v>
+        <v>giovanni01749778064330@gmail.com</v>
       </c>
       <c r="G5" t="str">
         <v>PASS</v>
@@ -531,10 +531,10 @@
         <v>1QyGVUpC</v>
       </c>
       <c r="F6" t="str">
-        <v>sylvia911749693411002@gmail.com</v>
+        <v>sylvia911749778067069@gmail.com</v>
       </c>
       <c r="G6" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="7">
@@ -554,10 +554,10 @@
         <v>grZSy1lE</v>
       </c>
       <c r="F7" t="str">
-        <v>hermina.heaney411749693411540@gmail.com</v>
+        <v>hermina.heaney411749778069853@gmail.com</v>
       </c>
       <c r="G7" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="8">
@@ -577,10 +577,10 @@
         <v>2JxDrvcZ</v>
       </c>
       <c r="F8" t="str">
-        <v>cordie691749693411544@gmail.com</v>
+        <v>cordie691749778072537@gmail.com</v>
       </c>
       <c r="G8" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="9">
@@ -600,10 +600,10 @@
         <v>F4LYvBjX</v>
       </c>
       <c r="F9" t="str">
-        <v>clare_oreilly1749693411547@gmail.com</v>
+        <v>clare_oreilly1749778075768@gmail.com</v>
       </c>
       <c r="G9" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="10">
@@ -623,15 +623,38 @@
         <v>TXoXmgmC</v>
       </c>
       <c r="F10" t="str">
-        <v>mitchell.hand1749693411570@hotmail.com</v>
+        <v>mitchell.hand1749778078433@hotmail.com</v>
       </c>
       <c r="G10" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Shank</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Shaz</v>
+      </c>
+      <c r="C11" t="str">
+        <v>shan.sjaz@gmail.com</v>
+      </c>
+      <c r="D11" t="str">
+        <v>+1 914-172-7233</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Absdgfhgshf</v>
+      </c>
+      <c r="F11" t="str">
+        <v>shan.sjaz1749778081594@gmail.com</v>
+      </c>
+      <c r="G11" t="str">
+        <v>PASS</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G11"/>
   </ignoredErrors>
 </worksheet>
 </file>